--- a/data/DOC-20251215-WA0003.xlsx
+++ b/data/DOC-20251215-WA0003.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Descargas\Acciona Facility Services\Aplicaciones Webs\mi-app-qr\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Descargas\Julio Cesar\Trabajo\Acciona Facility Services\Aplicaciones Webs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D9A484-3E07-42AF-B03F-689CD3784803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF49DCC-E0EF-418E-A2D0-0360F9FBFA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12045" yWindow="21480" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6311" uniqueCount="4389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6317" uniqueCount="4392">
   <si>
     <t>ID_ACTIVO_ARBOL</t>
   </si>
@@ -13187,6 +13192,15 @@
   </si>
   <si>
     <t>2465 MCS Steerable Wheel Divert</t>
+  </si>
+  <si>
+    <t>Muelle 111</t>
+  </si>
+  <si>
+    <t>Muelle 112</t>
+  </si>
+  <si>
+    <t>Muelle 113</t>
   </si>
 </sst>
 </file>
@@ -13485,7 +13499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3155"/>
+  <dimension ref="A1:C3158"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
@@ -48199,6 +48213,39 @@
         <v>4388</v>
       </c>
     </row>
+    <row r="3156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3156">
+        <v>273453</v>
+      </c>
+      <c r="B3156" t="s">
+        <v>4389</v>
+      </c>
+      <c r="C3156" t="s">
+        <v>4389</v>
+      </c>
+    </row>
+    <row r="3157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3157">
+        <v>273454</v>
+      </c>
+      <c r="B3157" t="s">
+        <v>4390</v>
+      </c>
+      <c r="C3157" t="s">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="3158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3158">
+        <v>273455</v>
+      </c>
+      <c r="B3158" t="s">
+        <v>4391</v>
+      </c>
+      <c r="C3158" t="s">
+        <v>4391</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
